--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>最终Boss</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+  </si>
+  <si>
+    <t>子弹</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1255,6 +1261,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10" spans="8:10">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>子弹</t>
+  </si>
+  <si>
+    <t>ParticleEffect</t>
+  </si>
+  <si>
+    <t>特效</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1272,6 +1278,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="11" spans="8:10">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -104,25 +104,37 @@
     <t>Monster</t>
   </si>
   <si>
-    <t>普通怪</t>
+    <t>普通</t>
   </si>
   <si>
     <t>EliteMonster</t>
   </si>
   <si>
-    <t>精英怪</t>
+    <t>精英</t>
   </si>
   <si>
     <t>LittleBoss</t>
   </si>
   <si>
-    <t>小Boss</t>
+    <t>统领</t>
   </si>
   <si>
     <t>FinalBoss</t>
   </si>
   <si>
-    <t>最终Boss</t>
+    <t>首领</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>ParticleEffect</t>
+  </si>
+  <si>
+    <t>特效</t>
   </si>
   <si>
     <t>Bullet</t>
@@ -131,10 +143,16 @@
     <t>子弹</t>
   </si>
   <si>
-    <t>ParticleEffect</t>
-  </si>
-  <si>
-    <t>特效</t>
+    <t>Cast</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>摄像机</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1289,6 +1307,39 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12" spans="8:10">
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="8:10">
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="8:10">
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -137,12 +137,6 @@
     <t>特效</t>
   </si>
   <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>子弹</t>
-  </si>
-  <si>
     <t>Cast</t>
   </si>
   <si>
@@ -153,6 +147,12 @@
   </si>
   <si>
     <t>摄像机</t>
+  </si>
+  <si>
+    <t>EnergyBlock</t>
+  </si>
+  <si>
+    <t>能量块</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1229,8 +1229,11 @@
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="8:10">
+    <row r="5" spans="8:11">
       <c r="H5" t="s">
         <v>22</v>
       </c>
@@ -1240,8 +1243,11 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="8:10">
+    <row r="6" spans="8:11">
       <c r="H6" t="s">
         <v>24</v>
       </c>
@@ -1251,8 +1257,11 @@
       <c r="J6">
         <v>2</v>
       </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" spans="8:10">
+    <row r="7" spans="8:11">
       <c r="H7" t="s">
         <v>26</v>
       </c>
@@ -1262,8 +1271,11 @@
       <c r="J7">
         <v>3</v>
       </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="8:10">
+    <row r="8" spans="8:11">
       <c r="H8" t="s">
         <v>28</v>
       </c>
@@ -1273,8 +1285,11 @@
       <c r="J8">
         <v>4</v>
       </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="9" spans="8:10">
+    <row r="9" spans="8:11">
       <c r="H9" t="s">
         <v>30</v>
       </c>
@@ -1284,8 +1299,11 @@
       <c r="J9">
         <v>5</v>
       </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" spans="8:11">
       <c r="H10" t="s">
         <v>32</v>
       </c>
@@ -1295,8 +1313,11 @@
       <c r="J10">
         <v>6</v>
       </c>
+      <c r="K10" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="11" spans="8:10">
+    <row r="11" spans="8:11">
       <c r="H11" t="s">
         <v>34</v>
       </c>
@@ -1306,8 +1327,11 @@
       <c r="J11">
         <v>7</v>
       </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="12" spans="8:10">
+    <row r="12" spans="8:11">
       <c r="H12" t="s">
         <v>36</v>
       </c>
@@ -1317,8 +1341,11 @@
       <c r="J12">
         <v>8</v>
       </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="13" spans="8:10">
+    <row r="13" spans="8:11">
       <c r="H13" t="s">
         <v>38</v>
       </c>
@@ -1328,8 +1355,11 @@
       <c r="J13">
         <v>9</v>
       </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="14" spans="8:10">
+    <row r="14" spans="8:11">
       <c r="H14" t="s">
         <v>40</v>
       </c>
@@ -1338,6 +1368,9 @@
       </c>
       <c r="J14">
         <v>10</v>
+      </c>
+      <c r="K14" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -92,13 +92,169 @@
     <t>None</t>
   </si>
   <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>玩家</t>
+    <t>无业游民</t>
+  </si>
+  <si>
+    <t>Famer</t>
+  </si>
+  <si>
+    <t>农民</t>
+  </si>
+  <si>
+    <t>LumberJack</t>
+  </si>
+  <si>
+    <t>樵夫</t>
+  </si>
+  <si>
+    <t>FisherMan</t>
+  </si>
+  <si>
+    <t>渔夫</t>
+  </si>
+  <si>
+    <t>Miner</t>
+  </si>
+  <si>
+    <t>矿工</t>
+  </si>
+  <si>
+    <t>Baker</t>
+  </si>
+  <si>
+    <t>面包师</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>厨师</t>
+  </si>
+  <si>
+    <t>BlackSmith</t>
+  </si>
+  <si>
+    <t>铁匠</t>
+  </si>
+  <si>
+    <t>Carpenter</t>
+  </si>
+  <si>
+    <t>木匠</t>
+  </si>
+  <si>
+    <t>Tailor</t>
+  </si>
+  <si>
+    <t>裁缝</t>
+  </si>
+  <si>
+    <t>Potter</t>
+  </si>
+  <si>
+    <t>陶工</t>
+  </si>
+  <si>
+    <t>Brewer</t>
+  </si>
+  <si>
+    <t>酿酒师</t>
+  </si>
+  <si>
+    <t>Jeweler</t>
+  </si>
+  <si>
+    <t>珠宝匠</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>Physician</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>教师</t>
+  </si>
+  <si>
+    <t>Priest</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>Soldier</t>
+  </si>
+  <si>
+    <t>士兵</t>
+  </si>
+  <si>
+    <t>CartDriver</t>
+  </si>
+  <si>
+    <t>车夫</t>
+  </si>
+  <si>
+    <t>Bard</t>
+  </si>
+  <si>
+    <t>吟游诗人</t>
+  </si>
+  <si>
+    <t>Actor</t>
+  </si>
+  <si>
+    <t>演员</t>
+  </si>
+  <si>
+    <t>Clerk</t>
+  </si>
+  <si>
+    <t>管理者</t>
+  </si>
+  <si>
+    <t>TxCollector</t>
+  </si>
+  <si>
+    <t>税务官</t>
+  </si>
+  <si>
+    <t>Scholar</t>
+  </si>
+  <si>
+    <t>学者</t>
+  </si>
+  <si>
+    <t>Noble</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>工程师</t>
+  </si>
+  <si>
+    <t>Adventurer</t>
+  </si>
+  <si>
+    <t>冒险者</t>
+  </si>
+  <si>
+    <t>Chief</t>
+  </si>
+  <si>
+    <t>小偷</t>
   </si>
 </sst>
 </file>
@@ -1061,8 +1217,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="23.625" customWidth="1"/>
@@ -1186,11 +1342,294 @@
       <c r="I5" t="s">
         <v>23</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
       <c r="K5" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="8:11">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11">
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11">
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="8:11">
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11">
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11">
+      <c r="H16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="8:11">
+      <c r="H17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="8:11">
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="8:11">
+      <c r="H19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="8:11">
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="8:11">
+      <c r="H21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="8:11">
+      <c r="H22" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="8:11">
+      <c r="H23" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="8:11">
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="8:11">
+      <c r="H25" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="8:11">
+      <c r="H26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I26" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="8:11">
+      <c r="H27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" t="s">
+        <v>67</v>
+      </c>
+      <c r="K27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="8:11">
+      <c r="H28" t="s">
+        <v>68</v>
+      </c>
+      <c r="I28" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="8:11">
+      <c r="H29" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="8:11">
+      <c r="H30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="8:11">
+      <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -89,7 +89,13 @@
     <t>cn.etetet.twsunit.UnitType</t>
   </si>
   <si>
-    <t>None</t>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>HomeLess</t>
   </si>
   <si>
     <t>无业游民</t>
@@ -1217,7 +1223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1342,6 +1348,7 @@
       <c r="I5" t="s">
         <v>23</v>
       </c>
+      <c r="J5"/>
       <c r="K5" t="s">
         <v>23</v>
       </c>
@@ -1630,6 +1637,17 @@
       </c>
       <c r="K31" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="8:11">
+      <c r="H32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
